--- a/从零开始学Slots/从零开始学Slots-40-基础篇-RandomWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-40-基础篇-RandomWild.xlsx
@@ -5968,6 +5968,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L167" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6526,5 +6529,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M60" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-40-基础篇-RandomWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-40-基础篇-RandomWild.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="177">
   <si>
     <r>
       <rPr>
@@ -4832,7 +4832,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4951,6 +4951,18 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6216,8 +6228,8 @@
       <c r="B19" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="20" t="s">
-        <v>134</v>
+      <c r="C19" s="30">
+        <v>3</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
@@ -6283,8 +6295,8 @@
       <c r="C23" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="D23" s="23" t="s">
-        <v>146</v>
+      <c r="D23" s="31">
+        <v>512</v>
       </c>
       <c r="E23" s="23"/>
       <c r="F23" s="23"/>
@@ -6355,8 +6367,8 @@
       <c r="B29" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="24" t="s">
-        <v>156</v>
+      <c r="C29" s="32">
+        <v>10000</v>
       </c>
       <c r="D29" s="15" t="n">
         <v>0</v>
@@ -6393,8 +6405,8 @@
       <c r="B31" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="C31" s="24" t="s">
-        <v>160</v>
+      <c r="C31" s="32">
+        <v>11111</v>
       </c>
       <c r="D31" s="15" t="n">
         <v>0</v>
@@ -6456,8 +6468,8 @@
       <c r="E36" s="14"/>
     </row>
     <row r="37" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
-        <v>170</v>
+      <c r="A37" s="30">
+        <v>512</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>171</v>
